--- a/bombus-system/docs/現況與問題比對分析_20260406.xlsx
+++ b/bombus-system/docs/現況與問題比對分析_20260406.xlsx
@@ -8,39 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alifrt/Desktop/Bombus/bombus-system/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8255F2AC-919E-6C44-9176-FE73DC252823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9851C6-A4D0-0747-BFE4-603A778BE84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0212版修訂需求總表" sheetId="1" r:id="rId1"/>
-    <sheet name="0206版需求" sheetId="4" r:id="rId2"/>
-    <sheet name="圖例說明" sheetId="2" r:id="rId3"/>
-    <sheet name="統計總覽" sheetId="3" r:id="rId4"/>
+    <sheet name="0206版需求" sheetId="2" r:id="rId2"/>
+    <sheet name="圖例說明" sheetId="3" r:id="rId3"/>
+    <sheet name="統計總覽" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'0206版需求'!$A$1:$M$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0212版修訂需求總表'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0212版修訂需求總表'!$A$1:$M$16</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="400">
   <si>
     <t>編號</t>
   </si>
@@ -73,6 +60,12 @@
   </si>
   <si>
     <t>修改難易度</t>
+  </si>
+  <si>
+    <t>修改狀態</t>
+  </si>
+  <si>
+    <t>修改說明</t>
   </si>
   <si>
     <t>D-01</t>
@@ -110,6 +103,12 @@
   </si>
   <si>
     <t>低</t>
+  </si>
+  <si>
+    <t>已修正</t>
+  </si>
+  <si>
+    <t>遵循 首頁 &gt; 模組 &gt; 子功能 &gt; pageTitle 的統一規則</t>
   </si>
   <si>
     <t>D-02</t>
@@ -366,12 +365,6 @@
     <t>今日待面試人選區</t>
   </si>
   <si>
-    <t>候選人列表上方加入「今天待面試人選」，面試官可一眼看出今日面試數量（面試官視角）。面試狀態保留：待面試、已面試。Tab調整為：待面試、已面試、全部</t>
-  </si>
-  <si>
-    <t>新增「今日面試摘要區」供面試官快速掌握當日面試；Tab 簡化為三個以面試為中心的狀態分類</t>
-  </si>
-  <si>
     <t>⚠️ 部分實作。
 ✅ 10 個狀態 Tab（job-candidates-page.component.ts:80-91）
 ✅ Stats 卡片（HTML:14-21）四個 KPI
@@ -442,6 +435,9 @@
     <t>最後決策功能需嚴格權限控制（僅人資/授權角色），並提供專屬的決策狀態篩選 Tab</t>
   </si>
   <si>
+    <t>✅ 已實作</t>
+  </si>
+  <si>
     <t>⚠️ 部分實作。
 ✅ 後端權限 requireFeaturePerm("L1.recruitment","edit")（recruitment.js:779）
 ✅ 前端路由 guard（employee.routes.ts:35-39）
@@ -463,6 +459,9 @@
     <t>決策是獨立頁面還是篩選視圖？權限需細粒度（L1.recruitment.decision）？Tab 如何調整？</t>
   </si>
   <si>
+    <t>拆分至獨立「面試決策」頁 (/employee/decision)，新增 L1.decision feature；RBAC：super_admin / subsidiary_admin / hr_manager = edit；dept_manager / employee = none。Tab 調整為 全部/待決策/已決策。</t>
+  </si>
+  <si>
     <t>D-13</t>
   </si>
   <si>
@@ -495,6 +494,9 @@
   </si>
   <si>
     <t>評分表呈現形式（全17項 or 摘要）？職缺薪資從哪取得？薪資核定需審批？是否統一用 hiring-decision-modal？</t>
+  </si>
+  <si>
+    <t>決策頁重構為：① 候選人基本資料 ② 職缺詳情（職等/薪資範圍/期望薪資/JD 摘要）③ 面試評分（只讀）④ AI 量化分析（只讀）⑤ 錄用決策 + 薪資核定（類型/金額，依 job.grade 關聯 grade_salary_levels 顯示範圍，超範圍警告但仍可送）。</t>
   </si>
   <si>
     <t>D-14</t>
@@ -544,9 +546,6 @@
     <t>完整的決策→入職流程需串連：決策核定 → 薪資輸入 → Offer Letter 產生與 Email 發送 → 候選人回覆 → 自動轉入入職管理模組</t>
   </si>
   <si>
-    <t>✅ 已實作</t>
-  </si>
-  <si>
     <t>✅ 核心鏈路已實作：
 ✅ 決策（recruitment.js:779）→ Offer Token（:796）→ 候選人回覆（:1101-1171，accepted→offer_accepted+Hired）
 ✅ HR 查看待入職（hr-onboarding.js:71-109 /pending-conversions）
@@ -568,76 +567,7 @@
     <t>入職指引包含什麼？到職日誰決定？初始密碼通知方式？Email 是否上線前必須？</t>
   </si>
   <si>
-    <t>圖例說明</t>
-  </si>
-  <si>
-    <t>功能已完成開發，可正常使用</t>
-  </si>
-  <si>
-    <t>基礎架構或資料模型已有，但缺少完整 UI 或部分功能</t>
-  </si>
-  <si>
-    <t>功能完全尚未開發或需大幅修改</t>
-  </si>
-  <si>
-    <t>編號區間</t>
-  </si>
-  <si>
-    <t>對應模組</t>
-  </si>
-  <si>
-    <t>D-01~D-09</t>
-  </si>
-  <si>
-    <t>D-10~D-11</t>
-  </si>
-  <si>
-    <t>D-12~D-15</t>
-  </si>
-  <si>
-    <t>修改難易度說明</t>
-  </si>
-  <si>
-    <t>純文字修改/欄位已有/功能已實作，工作量 1-2 天</t>
-  </si>
-  <si>
-    <t>需修改現有架構/新增 CRUD/跨模組整合，工作量 3-5 天</t>
-  </si>
-  <si>
-    <t>全新功能/複雜流程引擎/外部服務整合，工作量 1-2 週以上</t>
-  </si>
-  <si>
-    <t>修訂需求執行現況統計（Code Review 更新 2026/04/16）</t>
-  </si>
-  <si>
-    <t>合計</t>
-  </si>
-  <si>
-    <t>難易度:低</t>
-  </si>
-  <si>
-    <t>難易度:中</t>
-  </si>
-  <si>
-    <t>難易度:高</t>
-  </si>
-  <si>
-    <t>L1-員工檔案</t>
-  </si>
-  <si>
-    <t>L1-入職管理</t>
-  </si>
-  <si>
-    <t>L1-會議管理</t>
-  </si>
-  <si>
-    <t>L2-職等職級</t>
-  </si>
-  <si>
-    <t>L2-職務說明書</t>
-  </si>
-  <si>
-    <t>總計</t>
+    <t>新增主管簽核流程：HR 送簽 → subsidiary_admin 簽核 → offered（產 UUID offer link），可無限次退回重送。入職轉換（convert-candidate）要求 approval_status = APPROVED，既有資料 NONE 豁免。</t>
   </si>
   <si>
     <t>S-08</t>
@@ -828,6 +758,11 @@
     <t>照片來源（上傳 or 104）？是否需裁切？fallback 邏輯？隱私合規？</t>
   </si>
   <si>
+    <t>4 個頁面加入 @if(candidate.avatar) 判斷：有照片顯示 &lt;img&gt;，否則首字母
+Candidate 介面新增 avatar?: string 欄位
+4 個 SCSS 新增 .avatar-img 樣式（圓形裁切 + object-fit: cover）</t>
+  </si>
+  <si>
     <t>S-16</t>
   </si>
   <si>
@@ -838,6 +773,15 @@
   </si>
   <si>
     <t>在候選人詳情頁新增「聯繫記錄」區塊/Tab：可記錄每次電話/Email/面談的聯繫時間、方式、結果（如未接聯、已約面試、待回覆等），支援多人協作查看</t>
+  </si>
+  <si>
+    <t>✅ 已實作（人才庫完整）。
+✅ Model TalentContactHistory（talent-pool.model.ts:66-76）
+✅ DB talent_contact_history 表（:885-897）
+✅ UI：talent-pool-page:296-415「聯繫紀錄」Tab+新增 Modal(:525-610)
+✅ 待聯繫提醒（:366-377，1月未聯繫顯示「待聯繫」）
+✅ API：GET/POST contacts、PUT contact-reminder
+⚠️ 候選人詳情頁（profile-detail）無聯繫記錄</t>
   </si>
   <si>
     <t>features/employee/pages/talent-pool-page/
@@ -849,6 +793,12 @@
   </si>
   <si>
     <t>候選人詳情頁是否也需聯繫記錄？是否需支援編輯/刪除？</t>
+  </si>
+  <si>
+    <t>已實作</t>
+  </si>
+  <si>
+    <t>已實作於人才庫與再接觸管理</t>
   </si>
   <si>
     <t>S-17</t>
@@ -879,6 +829,9 @@
   </si>
   <si>
     <t>S-18</t>
+  </si>
+  <si>
+    <t>L1-員工檔案</t>
   </si>
   <si>
     <t>顯示任職年限</t>
@@ -907,6 +860,10 @@
   </si>
   <si>
     <t>顯示格式（X年Y月 or X.Y年）？列表也加欄？離職員工是否顯示？</t>
+  </si>
+  <si>
+    <t>employee-detail.component.ts 新增 getTenure() 方法（計算 X 年 Y 個月）
+employee-detail.component.html 在到職日下方新增「任職年限」欄位</t>
   </si>
   <si>
     <t>S-19</t>
@@ -977,6 +934,9 @@
     <t>S-21</t>
   </si>
   <si>
+    <t>L1-入職管理</t>
+  </si>
+  <si>
     <t>待入職/入職中狀態區分</t>
   </si>
   <si>
@@ -984,6 +944,14 @@
   </si>
   <si>
     <t>新進人員流程應區分兩個階段：「待入職」（已錄取尚未報到）和「入職中」（已報到正在辦理入職手續），不同狀態有不同的操作與顯示</t>
+  </si>
+  <si>
+    <t>✅ 已實作。
+✅ DB onboarding_status（:382），初始值 pending
+✅ 狀態列舉：pending(待入職)/in_progress(入職中)/completed(完成)，自動計算（:580-584）
+✅ 前端分「待入職候選人」和「入職中員工」兩區塊
+✅ 4 Tab（入職進度/文件管理/我的入職文件/簽核）
+⚠️ 狀態為被動更新（查看時才計算）</t>
   </si>
   <si>
     <t>server/src/routes/hr-onboarding.js (:384-467, :473-625)
@@ -996,6 +964,11 @@
     <t>是否需排程任務自動更新狀態？「待入職」精確定義？</t>
   </si>
   <si>
+    <t xml:space="preserve"> DB onboarding_status（:382），初始值 pending
+狀態列舉：pending(待入職)/in_progress(入職中)/completed(完成)，自動計算（:580-584）
+前端分「待入職候選人」和「入職中員工」兩區塊</t>
+  </si>
+  <si>
     <t>S-22</t>
   </si>
   <si>
@@ -1003,6 +976,15 @@
   </si>
   <si>
     <t>開發「入職文件清單檢核」，區分公司提供（合約、保密協議）與個人提供（身分證、證照）</t>
+  </si>
+  <si>
+    <t>建立入職文件檢核清單，明確分為兩大類：(1)公司提供文件（勞動合約、保密協議、員工手冊等）需員工簽署 (2)個人提供文件（身分證、學經歷證明、銀行帳號、體檢報告等）需員工上傳</t>
+  </si>
+  <si>
+    <t>✅ 已實作。
+✅ FIXED_DOCUMENT_TYPES 5 種（onboarding.model.ts:166-207）：id_card/bank_account/health_report/photo/education_cert，all required
+✅ 文件上傳完整：固定類型+自訂文件+狀態追蹤(pending→uploaded→approved→rejected)+查看/下載/刪除+進度計算
+⚠️ 未明確區分「公司提供」vs「個人提供」。公司文件走模板簽署系統，兩者合併顯示無標註</t>
   </si>
   <si>
     <t>features/employee/models/onboarding.model.ts (:112-220)
@@ -1016,6 +998,10 @@
     <t>UI 是否需區分公司/個人文件？固定類型改為可配置？退回重傳流程是否通順？</t>
   </si>
   <si>
+    <t>FIXED_DOCUMENT_TYPES 5 種（onboarding.model.ts:166-207）：id_card/bank_account/health_report/photo/education_cert，all required
+文件上傳完整：固定類型+自訂文件+狀態追蹤(pending→uploaded→approved→rejected)+查看/下載/刪除+進度計算</t>
+  </si>
+  <si>
     <t>S-23</t>
   </si>
   <si>
@@ -1045,6 +1031,9 @@
     <t>S-24</t>
   </si>
   <si>
+    <t>L1-會議管理</t>
+  </si>
+  <si>
     <t>五階段流程完整實作</t>
   </si>
   <si>
@@ -1052,6 +1041,16 @@
   </si>
   <si>
     <t>會議完整五階段生命週期：(1)準備（建立會議/議程/出席者）(2)議程確認 (3)會議進行（簽到/記錄）(4)會議結論（決議事項/負責人/截止日）(5)結論追蹤（進度更新/狀態管理）</t>
+  </si>
+  <si>
+    <t>✅ 已實作。
+✅ Model 完整：MeetingStatus(4態)/AgendaItemStatus(3態)/ConclusionStatus(4態)
+✅ UI 四種檢視（calendar/list/tracking/stats）
+✅ 簽到：QR Code+公開簽到頁+匯出
+✅ 議程討論含 discussionPoints
+✅ 結論追蹤：指定負責人/期限/進度更新
+✅ 後端完整 CRUD+權限控制
+⚠️ currentEmployeeId 硬編碼（:100-101）</t>
   </si>
   <si>
     <t>features/employee/pages/meeting-page/ (1667行)
@@ -1063,6 +1062,14 @@
   </si>
   <si>
     <t>「五階段」具體指哪五個？currentEmployeeId 何時整合？公開簽到安全性？</t>
+  </si>
+  <si>
+    <t>Model 完整：MeetingStatus(4態)/AgendaItemStatus(3態)/ConclusionStatus(4態)
+UI 四種檢視（calendar/list/tracking/stats）
+簽到：QR Code+公開簽到頁+匯出
+議程討論含 discussionPoints
+結論追蹤：指定負責人/期限/進度更新
+後端完整 CRUD+權限控制</t>
   </si>
   <si>
     <t>S-25</t>
@@ -1100,12 +1107,21 @@
     <t>S-27</t>
   </si>
   <si>
+    <t>L2-職等職級</t>
+  </si>
+  <si>
     <t>矩陣顯示改用 Tab</t>
   </si>
   <si>
     <t>職等職級矩陣下拉資料改成用 Tab 的方式顯示，以方便閱讀。可參考 L2 文件所提供的網址修訂</t>
   </si>
   <si>
+    <t>職等職級矩陣頁面的資料呈現方式從下拉選單改為 Tab 標籤式切換，每個 Tab 對應一個職等，方便使用者直覺瀏覽與比較</t>
+  </si>
+  <si>
+    <t>✅ 已實作。5 個主 Tab（矩陣/職涯路徑/AI 規劃/待審核/變更歷史）+動態子標籤（overview+各軌道明細）。雙軌制表格+卡片式職涯路徑+AI 雷達圖</t>
+  </si>
+  <si>
     <t>features/competency/pages/grade-matrix-page/</t>
   </si>
   <si>
@@ -1113,6 +1129,9 @@
   </si>
   <si>
     <t>確認 Tab 呈現是否符合預期？</t>
+  </si>
+  <si>
+    <t>5 個主 Tab（矩陣/職涯路徑/AI 規劃/待審核/變更歷史）+動態子標籤（overview+各軌道明細）。雙軌制表格+卡片式職涯路徑+AI 雷達圖</t>
   </si>
   <si>
     <t>S-28</t>
@@ -1175,7 +1194,16 @@
     <t>S-30</t>
   </si>
   <si>
+    <t>L2-職務說明書</t>
+  </si>
+  <si>
     <t>JD 封存流程</t>
+  </si>
+  <si>
+    <t>職務說明書管理，發布要審核但封存不用審核？流程應再跟邦鉑確認或整理情境流程</t>
+  </si>
+  <si>
+    <t>需釐清 JD 的完整狀態流程：草稿→審核中→已發布→已封存。目前發布需審核但封存不需，需確認封存是否也應經過審核（避免誤操作影響使用中的 JD）</t>
   </si>
   <si>
     <t>✅ 已實作。JD 完整狀態流 draft→pending_review→published→archived。封存 API（job-descriptions.js:392-427），僅 published 可封存，不需審核，更新版本 effective_until。封存後顯示「僅供查閱」。無還原功能</t>
@@ -1188,866 +1216,7 @@
     <t>低風險。流程完整</t>
   </si>
   <si>
-    <t>S-31</t>
-  </si>
-  <si>
-    <t>AKS 中文標籤</t>
-  </si>
-  <si>
-    <t>將 A, K, S 代碼增加明確中文標籤（A-態度、K-知識、S-技能），提升可讀性</t>
-  </si>
-  <si>
-    <t>職能分類代碼 A/K/S 旁邊加上完整中文名稱「態度/知識/技能」，讓不熟悉代碼的使用者也能直觀理解</t>
-  </si>
-  <si>
-    <t>features/competency/pages/framework-page/</t>
-  </si>
-  <si>
-    <t>無風險</t>
-  </si>
-  <si>
-    <t>是否改 AKS 順序？中文是否符合客戶用語？</t>
-  </si>
-  <si>
-    <t>S-32</t>
-  </si>
-  <si>
-    <t>JD 模板複製</t>
-  </si>
-  <si>
-    <t>提供 JD 模板複製功能。創建相似崗位（如專員與資深專員）的 JD 時，允許用戶複製現有模板並在此基礎上修改</t>
-  </si>
-  <si>
-    <t>在 JD 列表頁面新增「複製」操作按鈕：選擇既有 JD 後一鍵複製為新草稿，預填所有欄位，使用者僅需修改差異部分（如職稱、職等），大幅提升建立相似 JD 的效率</t>
-  </si>
-  <si>
-    <t>features/competency/pages/create-jd-page/ (:482-609)</t>
-  </si>
-  <si>
-    <t>JD 列表需獨立「複製」按鈕？複製時哪些欄位清空？</t>
-  </si>
-  <si>
-    <t>S-33</t>
-  </si>
-  <si>
-    <t>JD 匯入（PDF/CSV）</t>
-  </si>
-  <si>
-    <t>支援通過上傳 PDF 或 CSV 文件導入現有 JD。可引入 AI 技術輔助識別文件內容並自動填充至對應欄位</t>
-  </si>
-  <si>
-    <t>新增 JD 匯入功能：可上傳 PDF 或 CSV 格式的既有職務說明書，系統以 AI 解析文件內容並自動對應填入各欄位（職稱、職責、資格要求等），減少手動輸入</t>
-  </si>
-  <si>
-    <t>❌ 未實作。無 PDF/CSV 匯入。只有 PDF 匯出（pdf-export.service.ts jsPDF）。AI 填充為 Mock（:438-479 setTimeout 模擬）</t>
-  </si>
-  <si>
-    <t>需新增：create-jd-page 匯入模式
-需新增：匯入 API
-需新增：PDF/CSV 解析服務</t>
-  </si>
-  <si>
-    <t>高風險。PDF 解析不可控。AI 需 LLM API 費用</t>
-  </si>
-  <si>
-    <t>PDF 是解析既有文件 or 指定模板？CSV 格式定義？AI 是否接入？</t>
-  </si>
-  <si>
-    <t>S-34</t>
-  </si>
-  <si>
-    <t>部門職位對照表與組織圖整合</t>
-  </si>
-  <si>
-    <t>將「部門職位對照表」與「集團組織圖」功能整合。在組織圖界面中支援直接編輯各職位的職等（Grade）、職級（BS）以及對應的薪資範圍，確保數據源統一</t>
-  </si>
-  <si>
-    <t>組織架構圖中的每個職位節點應可直接查看/編輯其職等、職級（BS碼）及薪資範圍，實現組織架構與職等薪資的單一數據源管理</t>
-  </si>
-  <si>
-    <t>⚠️ 部分實作。
-✅ 部門職位對照表（grade-matrix-page:228-291，部門×職等矩陣+篩選）
-✅ DB department_positions 表（:1561-1570）
-❌ 組織圖僅有 employee-management-page 無圖元件
-❌ org-structure-page 在 tenant-admin 與 competency 無資料連動</t>
-  </si>
-  <si>
-    <t>features/competency/pages/grade-matrix-page/ (:228-291)
-features/organization/
-features/tenant-admin/pages/org-structure-page/</t>
-  </si>
-  <si>
-    <t>中風險。跨模組資料整合可能同步問題</t>
-  </si>
-  <si>
-    <t>整合方式？部門資料來源統一？組織圖上顯示職位 or 點擊進對照表？</t>
-  </si>
-  <si>
-    <t>S-35</t>
-  </si>
-  <si>
-    <t>晉升條件改為參考標準</t>
-  </si>
-  <si>
-    <t>晉升條件（如績效基准、必備技能、必修課程）應作為「參考標準」而非「強制門檻」。系統應允許企業自定義各項條件的權重，並保留人工決策的最終權力</t>
-  </si>
-  <si>
-    <t>晉升條件定位為「參考指標」而非系統自動卡控的「硬門檻」：企業可自訂各條件（績效/技能/課程）的權重比例，最終晉升決策仍由人工判斷，系統僅提供達標率參考</t>
-  </si>
-  <si>
-    <t>❌ 未實作。UI 6 處+TS 4 處仍用「績效門檻」。performanceThreshold 定義 number 但實際用 A+/A/B+/B 字串（型別不匹配 bug）。promotion_criteria 無 weight 欄位</t>
-  </si>
-  <si>
-    <t>features/competency/components/promotion-criteria-edit-modal/
-features/competency/components/track-detail-edit-panel/
-features/competency/pages/grade-matrix-page/
-server/src/db/tenant-schema.js</t>
-  </si>
-  <si>
-    <t>低-中風險。用語修改不影響功能，但 number vs string 型別是 bug。權重需新增資料模型</t>
-  </si>
-  <si>
-    <t>「參考標準」是改用語 or 改機制？加權重？performanceThreshold 型別修正？</t>
-  </si>
-  <si>
-    <t>S-36</t>
-  </si>
-  <si>
-    <t>績效門檻改名為績效基准</t>
-  </si>
-  <si>
-    <t>將系統中的「績效門檻」統一修改為「績效基准」，避免負面暗示，提升使用者體驗</t>
-  </si>
-  <si>
-    <t>❌ 未實作。「績效門檻」出現 10 處：UI 6 處（HTML）+ TS 4 處。DB performance_threshold 未改名。TS performanceThreshold 未改名</t>
-  </si>
-  <si>
-    <t>同 S-35 影響範圍</t>
-  </si>
-  <si>
-    <t>低風險。純文字替換 10 處。DB 欄位改需 migration</t>
-  </si>
-  <si>
-    <t>「績效基准」or「績效基準」（簡繁）？DB 欄位改名 or 只改 UI？</t>
-  </si>
-  <si>
-    <t>全系統搜尋並替換「績效門檻」一詞為「績效基准」（或「績效基準」），包含前端 UI 文字、後端 API 回應、資料庫欄位註解等，消除「門檻=卡關」的負面暗示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改狀態</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已修正</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遵循 首頁 &gt; 模組 &gt; 子功能 &gt; pageTitle 的統一規則</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4 個頁面加入 @if(candidate.avatar) 判斷：有照片顯示 &lt;img&gt;，否則首字母
-Candidate 介面新增 avatar?: string 欄位
-4 個 SCSS 新增 .avatar-img 樣式（圓形裁切 + object-fit: cover）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>employee-detail.component.ts 新增 getTenure() 方法（計算 X 年 Y 個月）
-employee-detail.component.html 在到職日下方新增「任職年限」欄位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 已實作（人才庫完整）。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> Model TalentContactHistory（talent-pool.model.ts:66-76）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> DB talent_contact_history 表（:885-897）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> UI：talent-pool-page:296-415「聯繫紀錄」Tab+新增 Modal(:525-610)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 待聯繫提醒（:366-377，1月未聯繫顯示「待聯繫」）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> API：GET/POST contacts、PUT contact-reminder
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 候選人詳情頁（profile-detail）無聯繫記錄</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已實作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前端 HTML 6 處：promotion-criteria-edit-modal、track-detail-edit-panel、grade-matrix-page
-前端 TS 4 處：驗證訊息、變更描述、差異比較
-後端 DB：tenant-schema.js performance_threshold 加上中文註解</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 已實作。KSA 中文標籤：K=知識、S=技能、A=態度（framework-page:350-356）。Tab 描述含完整中英文。CSS 色碼區分（:727-737, :808-821）。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 系統用 KSA 順序非 AKS</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KSA 中文標籤：K=知識、S=技能、A=態度（framework-page:350-356）。Tab 描述含完整中英文。CSS 色碼區分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>已實作於人才庫與再接觸管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>修改說明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 已實作。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> DB onboarding_status（:382），初始值 pending
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 狀態列舉：pending(待入職)/in_progress(入職中)/completed(完成)，自動計算（:580-584）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 前端分「待入職候選人」和「入職中員工」兩區塊
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 4 Tab（入職進度/文件管理/我的入職文件/簽核）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 狀態為被動更新（查看時才計算）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> DB onboarding_status（:382），初始值 pending
-狀態列舉：pending(待入職)/in_progress(入職中)/completed(完成)，自動計算（:580-584）
-前端分「待入職候選人」和「入職中員工」兩區塊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>建立入職文件檢核清單，明確分為兩大類：(1)公司提供文件（勞動合約、保密協議、員工手冊等）需員工簽署 (2)個人提供文件（身分證、學經歷證明、銀行帳號、體檢報告等）需員工上傳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 已實作。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> FIXED_DOCUMENT_TYPES 5 種（onboarding.model.ts:166-207）：id_card/bank_account/health_report/photo/education_cert，all required
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 文件上傳完整：固定類型+自訂文件+狀態追蹤(pending→uploaded→approved→rejected)+查看/下載/刪除+進度計算
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 未明確區分「公司提供」vs「個人提供」。公司文件走模板簽署系統，兩者合併顯示無標註</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FIXED_DOCUMENT_TYPES 5 種（onboarding.model.ts:166-207）：id_card/bank_account/health_report/photo/education_cert，all required
-文件上傳完整：固定類型+自訂文件+狀態追蹤(pending→uploaded→approved→rejected)+查看/下載/刪除+進度計算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 已實作。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> Model 完整：MeetingStatus(4態)/AgendaItemStatus(3態)/ConclusionStatus(4態)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> UI 四種檢視（calendar/list/tracking/stats）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 簽到：QR Code+公開簽到頁+匯出
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 議程討論含 discussionPoints
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 結論追蹤：指定負責人/期限/進度更新
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 後端完整 CRUD+權限控制
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> currentEmployeeId 硬編碼（:100-101）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model 完整：MeetingStatus(4態)/AgendaItemStatus(3態)/ConclusionStatus(4態)
-UI 四種檢視（calendar/list/tracking/stats）
-簽到：QR Code+公開簽到頁+匯出
-議程討論含 discussionPoints
-結論追蹤：指定負責人/期限/進度更新
-後端完整 CRUD+權限控制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>職等職級矩陣頁面的資料呈現方式從下拉選單改為 Tab 標籤式切換，每個 Tab 對應一個職等，方便使用者直覺瀏覽與比較</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 已實作。5 個主 Tab（矩陣/職涯路徑/AI 規劃/待審核/變更歷史）+動態子標籤（overview+各軌道明細）。雙軌制表格+卡片式職涯路徑+AI 雷達圖</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5 個主 Tab（矩陣/職涯路徑/AI 規劃/待審核/變更歷史）+動態子標籤（overview+各軌道明細）。雙軌制表格+卡片式職涯路徑+AI 雷達圖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Apple Color Emoji"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> 已實作。create-jd-page「匯入模版」模式（:38-67）。下拉選單列出現有 JD，套用後深拷貝並清空 positionCode。JD 列表有 createNewVersion（版本管理）。後端無獨立 clone API</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create-jd-page「匯入模版」模式（:38-67）。下拉選單列出現有 JD，套用後深拷貝並清空 positionCode。JD 列表有 createNewVersion（版本管理）。後端無獨立 clone API</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>職務說明書管理，發布要審核但封存不用審核？流程應再跟邦鉑確認或整理情境流程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需釐清 JD 的完整狀態流程：草稿→審核中→已發布→已封存。目前發布需審核但封存不需，需確認封存是否也應經過審核（避免誤操作影響使用中的 JD）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>封存後需「取消封存」？封存加確認彈窗？封存 JD 對應在職員工？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>後端新增：jobdescriptions.js	POST /:id/unarchive API：archived → published，清除版本歷史的封存時間
@@ -2057,6 +1226,243 @@
 操作流程：
 封存：點擊「封存」→ 彈出確認視窗「封存後此職務說明書將無法編輯或發佈，確定要封存嗎？」→ 確認後封存
 取消封存：封存後顯示「取消封存」按鈕 → 點擊後彈出確認 → 狀態恢復為「已發佈」</t>
+  </si>
+  <si>
+    <t>S-31</t>
+  </si>
+  <si>
+    <t>AKS 中文標籤</t>
+  </si>
+  <si>
+    <t>將 A, K, S 代碼增加明確中文標籤（A-態度、K-知識、S-技能），提升可讀性</t>
+  </si>
+  <si>
+    <t>職能分類代碼 A/K/S 旁邊加上完整中文名稱「態度/知識/技能」，讓不熟悉代碼的使用者也能直觀理解</t>
+  </si>
+  <si>
+    <t>✅ 已實作。KSA 中文標籤：K=知識、S=技能、A=態度（framework-page:350-356）。Tab 描述含完整中英文。CSS 色碼區分（:727-737, :808-821）。⚠️ 系統用 KSA 順序非 AKS</t>
+  </si>
+  <si>
+    <t>features/competency/pages/framework-page/</t>
+  </si>
+  <si>
+    <t>無風險</t>
+  </si>
+  <si>
+    <t>是否改 AKS 順序？中文是否符合客戶用語？</t>
+  </si>
+  <si>
+    <t>KSA 中文標籤：K=知識、S=技能、A=態度（framework-page:350-356）。Tab 描述含完整中英文。CSS 色碼區分</t>
+  </si>
+  <si>
+    <t>S-32</t>
+  </si>
+  <si>
+    <t>JD 模板複製</t>
+  </si>
+  <si>
+    <t>提供 JD 模板複製功能。創建相似崗位（如專員與資深專員）的 JD 時，允許用戶複製現有模板並在此基礎上修改</t>
+  </si>
+  <si>
+    <t>在 JD 列表頁面新增「複製」操作按鈕：選擇既有 JD 後一鍵複製為新草稿，預填所有欄位，使用者僅需修改差異部分（如職稱、職等），大幅提升建立相似 JD 的效率</t>
+  </si>
+  <si>
+    <t>✅ 已實作。create-jd-page「匯入模版」模式（:38-67）。下拉選單列出現有 JD，套用後深拷貝並清空 positionCode。JD 列表有 createNewVersion（版本管理）。後端無獨立 clone API</t>
+  </si>
+  <si>
+    <t>features/competency/pages/create-jd-page/ (:482-609)</t>
+  </si>
+  <si>
+    <t>JD 列表需獨立「複製」按鈕？複製時哪些欄位清空？</t>
+  </si>
+  <si>
+    <t>create-jd-page「匯入模版」模式（:38-67）。下拉選單列出現有 JD，套用後深拷貝並清空 positionCode。JD 列表有 createNewVersion（版本管理）。後端無獨立 clone API</t>
+  </si>
+  <si>
+    <t>S-33</t>
+  </si>
+  <si>
+    <t>JD 匯入（PDF/CSV）</t>
+  </si>
+  <si>
+    <t>支援通過上傳 PDF 或 CSV 文件導入現有 JD。可引入 AI 技術輔助識別文件內容並自動填充至對應欄位</t>
+  </si>
+  <si>
+    <t>新增 JD 匯入功能：可上傳 PDF 或 CSV 格式的既有職務說明書，系統以 AI 解析文件內容並自動對應填入各欄位（職稱、職責、資格要求等），減少手動輸入</t>
+  </si>
+  <si>
+    <t>❌ 未實作。無 PDF/CSV 匯入。只有 PDF 匯出（pdf-export.service.ts jsPDF）。AI 填充為 Mock（:438-479 setTimeout 模擬）</t>
+  </si>
+  <si>
+    <t>需新增：create-jd-page 匯入模式
+需新增：匯入 API
+需新增：PDF/CSV 解析服務</t>
+  </si>
+  <si>
+    <t>高風險。PDF 解析不可控。AI 需 LLM API 費用</t>
+  </si>
+  <si>
+    <t>PDF 是解析既有文件 or 指定模板？CSV 格式定義？AI 是否接入？</t>
+  </si>
+  <si>
+    <t>S-34</t>
+  </si>
+  <si>
+    <t>部門職位對照表與組織圖整合</t>
+  </si>
+  <si>
+    <t>將「部門職位對照表」與「集團組織圖」功能整合。在組織圖界面中支援直接編輯各職位的職等（Grade）、職級（BS）以及對應的薪資範圍，確保數據源統一</t>
+  </si>
+  <si>
+    <t>組織架構圖中的每個職位節點應可直接查看/編輯其職等、職級（BS碼）及薪資範圍，實現組織架構與職等薪資的單一數據源管理</t>
+  </si>
+  <si>
+    <t>⚠️ 部分實作。
+✅ 部門職位對照表（grade-matrix-page:228-291，部門×職等矩陣+篩選）
+✅ DB department_positions 表（:1561-1570）
+❌ 組織圖僅有 employee-management-page 無圖元件
+❌ org-structure-page 在 tenant-admin 與 competency 無資料連動</t>
+  </si>
+  <si>
+    <t>features/competency/pages/grade-matrix-page/ (:228-291)
+features/organization/
+features/tenant-admin/pages/org-structure-page/</t>
+  </si>
+  <si>
+    <t>中風險。跨模組資料整合可能同步問題</t>
+  </si>
+  <si>
+    <t>整合方式？部門資料來源統一？組織圖上顯示職位 or 點擊進對照表？</t>
+  </si>
+  <si>
+    <t>S-35</t>
+  </si>
+  <si>
+    <t>晉升條件改為參考標準</t>
+  </si>
+  <si>
+    <t>晉升條件（如績效基准、必備技能、必修課程）應作為「參考標準」而非「強制門檻」。系統應允許企業自定義各項條件的權重，並保留人工決策的最終權力</t>
+  </si>
+  <si>
+    <t>晉升條件定位為「參考指標」而非系統自動卡控的「硬門檻」：企業可自訂各條件（績效/技能/課程）的權重比例，最終晉升決策仍由人工判斷，系統僅提供達標率參考</t>
+  </si>
+  <si>
+    <t>❌ 未實作。UI 6 處+TS 4 處仍用「績效門檻」。performanceThreshold 定義 number 但實際用 A+/A/B+/B 字串（型別不匹配 bug）。promotion_criteria 無 weight 欄位</t>
+  </si>
+  <si>
+    <t>features/competency/components/promotion-criteria-edit-modal/
+features/competency/components/track-detail-edit-panel/
+features/competency/pages/grade-matrix-page/
+server/src/db/tenant-schema.js</t>
+  </si>
+  <si>
+    <t>低-中風險。用語修改不影響功能，但 number vs string 型別是 bug。權重需新增資料模型</t>
+  </si>
+  <si>
+    <t>「參考標準」是改用語 or 改機制？加權重？performanceThreshold 型別修正？</t>
+  </si>
+  <si>
+    <t>S-36</t>
+  </si>
+  <si>
+    <t>績效門檻改名為績效基准</t>
+  </si>
+  <si>
+    <t>將系統中的「績效門檻」統一修改為「績效基准」，避免負面暗示，提升使用者體驗</t>
+  </si>
+  <si>
+    <t>全系統搜尋並替換「績效門檻」一詞為「績效基准」（或「績效基準」），包含前端 UI 文字、後端 API 回應、資料庫欄位註解等，消除「門檻=卡關」的負面暗示</t>
+  </si>
+  <si>
+    <t>❌ 未實作。「績效門檻」出現 10 處：UI 6 處（HTML）+ TS 4 處。DB performance_threshold 未改名。TS performanceThreshold 未改名</t>
+  </si>
+  <si>
+    <t>同 S-35 影響範圍</t>
+  </si>
+  <si>
+    <t>低風險。純文字替換 10 處。DB 欄位改需 migration</t>
+  </si>
+  <si>
+    <t>「績效基准」or「績效基準」（簡繁）？DB 欄位改名 or 只改 UI？</t>
+  </si>
+  <si>
+    <t>前端 HTML 6 處：promotion-criteria-edit-modal、track-detail-edit-panel、grade-matrix-page
+前端 TS 4 處：驗證訊息、變更描述、差異比較
+後端 DB：tenant-schema.js performance_threshold 加上中文註解</t>
+  </si>
+  <si>
+    <t>圖例說明</t>
+  </si>
+  <si>
+    <t>功能已完成開發，可正常使用</t>
+  </si>
+  <si>
+    <t>基礎架構或資料模型已有，但缺少完整 UI 或部分功能</t>
+  </si>
+  <si>
+    <t>功能完全尚未開發或需大幅修改</t>
+  </si>
+  <si>
+    <t>編號區間</t>
+  </si>
+  <si>
+    <t>對應模組</t>
+  </si>
+  <si>
+    <t>D-01~D-09</t>
+  </si>
+  <si>
+    <t>D-10~D-11</t>
+  </si>
+  <si>
+    <t>D-12~D-15</t>
+  </si>
+  <si>
+    <t>修改難易度說明</t>
+  </si>
+  <si>
+    <t>純文字修改/欄位已有/功能已實作，工作量 1-2 天</t>
+  </si>
+  <si>
+    <t>需修改現有架構/新增 CRUD/跨模組整合，工作量 3-5 天</t>
+  </si>
+  <si>
+    <t>全新功能/複雜流程引擎/外部服務整合，工作量 1-2 週以上</t>
+  </si>
+  <si>
+    <t>修訂需求執行現況統計（Code Review 更新 2026/04/16）</t>
+  </si>
+  <si>
+    <t>合計</t>
+  </si>
+  <si>
+    <t>難易度:低</t>
+  </si>
+  <si>
+    <t>難易度:中</t>
+  </si>
+  <si>
+    <t>難易度:高</t>
+  </si>
+  <si>
+    <t>總計</t>
+  </si>
+  <si>
+    <t>候選人列表上方加入「今天待面試人選」，面試官可一眼看出今日面試數量（面試官視角）。面試狀態保留：待面試、已面試。Tab調整為：待面試、已面試、全部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L1-AI智能面試</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增「今日面試摘要區」供面試官快速掌握當日面試；Tab 簡化為三個以面試為中心的狀態分類</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顯示時間由「投遞日」改為「最新面試時間」（yyyy-MM-dd HH:mm 含時刻）
+AI 智能面試頁新增面試日期篩選：日期選擇器 + 快速 tabs（全部 / 今日 / 近 3 天 / 近 7 天）
+AI 智能面試頁不再顯示已進入決策階段的候選人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2064,7 +1470,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2149,13 +1555,6 @@
       <b/>
       <sz val="10"/>
       <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Apple Color Emoji"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
@@ -2279,7 +1678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2363,7 +1762,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2413,6 +1812,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2716,6 +2130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
@@ -2727,11 +2142,11 @@
     <col min="7" max="7" width="55" customWidth="1"/>
     <col min="8" max="10" width="40" customWidth="1"/>
     <col min="11" max="11" width="20.3984375" customWidth="1"/>
-    <col min="12" max="12" width="15.3984375" style="35" customWidth="1"/>
-    <col min="13" max="13" width="73.19921875" style="35" customWidth="1"/>
+    <col min="12" max="12" width="15.3984375" style="51" customWidth="1"/>
+    <col min="13" max="13" width="73.19921875" style="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="35" customFormat="1" ht="18">
+    <row r="1" spans="1:13" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -2766,579 +2181,602 @@
         <v>10</v>
       </c>
       <c r="L1" s="47" t="s">
-        <v>367</v>
-      </c>
-      <c r="M1" s="48" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="126">
+        <v>11</v>
+      </c>
+      <c r="M1" s="52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="126" hidden="1" customHeight="1">
       <c r="A2" s="26" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="144" customHeight="1">
+      <c r="A3" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="26" t="s">
+      <c r="C3" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="50"/>
+      <c r="M3" s="53"/>
+    </row>
+    <row r="4" spans="1:13" ht="144" hidden="1" customHeight="1">
+      <c r="A4" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="33" t="s">
-        <v>368</v>
-      </c>
-      <c r="M2" s="46" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="144">
-      <c r="A3" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-    </row>
-    <row r="4" spans="1:13" ht="144">
-      <c r="A4" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>16</v>
-      </c>
       <c r="G4" s="26" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K4" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L4" s="34"/>
       <c r="M4" s="34"/>
     </row>
-    <row r="5" spans="1:13" ht="180">
+    <row r="5" spans="1:13" ht="180" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E5" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="50"/>
+      <c r="M5" s="53"/>
+    </row>
+    <row r="6" spans="1:13" ht="126" hidden="1" customHeight="1">
+      <c r="A6" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="31" t="s">
         <v>44</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-    </row>
-    <row r="6" spans="1:13" ht="126">
-      <c r="A6" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="K6" s="31" t="s">
-        <v>40</v>
       </c>
       <c r="L6" s="34"/>
       <c r="M6" s="34"/>
     </row>
-    <row r="7" spans="1:13" ht="126">
+    <row r="7" spans="1:13" ht="126" hidden="1" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L7" s="34"/>
       <c r="M7" s="34"/>
     </row>
-    <row r="8" spans="1:13" ht="144">
+    <row r="8" spans="1:13" ht="144" customHeight="1">
       <c r="A8" s="26" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-    </row>
-    <row r="9" spans="1:13" ht="108">
+        <v>35</v>
+      </c>
+      <c r="L8" s="50"/>
+      <c r="M8" s="53"/>
+    </row>
+    <row r="9" spans="1:13" ht="108" hidden="1" customHeight="1">
       <c r="A9" s="26" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L9" s="34"/>
       <c r="M9" s="34"/>
     </row>
-    <row r="10" spans="1:13" ht="180">
+    <row r="10" spans="1:13" ht="180" customHeight="1">
       <c r="A10" s="26" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-    </row>
-    <row r="11" spans="1:13" ht="144">
+        <v>35</v>
+      </c>
+      <c r="L10" s="50"/>
+      <c r="M10" s="53"/>
+    </row>
+    <row r="11" spans="1:13" ht="144" customHeight="1">
       <c r="A11" s="26" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>90</v>
+        <v>397</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>92</v>
+        <v>396</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>93</v>
+        <v>398</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G11" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="53" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="234" hidden="1" customHeight="1">
+      <c r="A12" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="K11" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-    </row>
-    <row r="12" spans="1:13" ht="234">
-      <c r="A12" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>90</v>
-      </c>
       <c r="C12" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K12" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L12" s="34"/>
       <c r="M12" s="34"/>
     </row>
-    <row r="13" spans="1:13" ht="216">
+    <row r="13" spans="1:13" ht="216" customHeight="1">
       <c r="A13" s="26" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D13" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="J13" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="53" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="198" customHeight="1">
+      <c r="A14" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="E13" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="I13" s="26" t="s">
+      <c r="C14" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="J13" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-    </row>
-    <row r="14" spans="1:13" ht="198">
-      <c r="A14" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>16</v>
-      </c>
       <c r="G14" s="26" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K14" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-    </row>
-    <row r="15" spans="1:13" ht="180">
+        <v>35</v>
+      </c>
+      <c r="L14" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="53" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="180" hidden="1" customHeight="1">
       <c r="A15" s="26" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G15" s="26" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H15" s="26" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K15" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="34"/>
     </row>
-    <row r="16" spans="1:13" ht="216">
+    <row r="16" spans="1:13" ht="216" customHeight="1">
       <c r="A16" s="26" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H16" s="26" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J16" s="26" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
+        <v>35</v>
+      </c>
+      <c r="L16" s="50" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="53" t="s">
+        <v>144</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M16" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="中"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
@@ -3357,7 +2795,7 @@
     <col min="13" max="13" width="83.59765625" style="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="35" customFormat="1" ht="18">
+    <row r="1" spans="1:13" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
@@ -3392,712 +2830,712 @@
         <v>10</v>
       </c>
       <c r="L1" s="47" t="s">
-        <v>367</v>
+        <v>11</v>
       </c>
       <c r="M1" s="48" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="72" hidden="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="72" hidden="1" customHeight="1">
       <c r="A2" s="26" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I2" s="39" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="K2" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L2" s="41"/>
       <c r="M2" s="41"/>
     </row>
-    <row r="3" spans="1:13" ht="126" hidden="1">
+    <row r="3" spans="1:13" ht="126" customHeight="1">
       <c r="A3" s="26" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="43" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="I3" s="39" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="J3" s="40" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L3" s="41"/>
       <c r="M3" s="41"/>
     </row>
-    <row r="4" spans="1:13" ht="72" hidden="1">
+    <row r="4" spans="1:13" ht="72" customHeight="1">
       <c r="A4" s="26" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="I4" s="39" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="J4" s="40" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L4" s="41"/>
       <c r="M4" s="41"/>
     </row>
-    <row r="5" spans="1:13" ht="54" hidden="1">
+    <row r="5" spans="1:13" ht="54" hidden="1" customHeight="1">
       <c r="A5" s="26" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>193</v>
+        <v>174</v>
       </c>
       <c r="I5" s="39" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="J5" s="40" t="s">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="K5" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L5" s="41"/>
       <c r="M5" s="41"/>
     </row>
-    <row r="6" spans="1:13" ht="54" hidden="1">
+    <row r="6" spans="1:13" ht="54" hidden="1" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="I6" s="39" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="J6" s="40" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="K6" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L6" s="41"/>
       <c r="M6" s="41"/>
     </row>
-    <row r="7" spans="1:13" ht="72" hidden="1">
+    <row r="7" spans="1:13" ht="72" hidden="1" customHeight="1">
       <c r="A7" s="26" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G7" s="43" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="I7" s="39" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="J7" s="40" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L7" s="41"/>
       <c r="M7" s="41"/>
     </row>
-    <row r="8" spans="1:13" ht="108">
+    <row r="8" spans="1:13" ht="108" hidden="1" customHeight="1">
       <c r="A8" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="I8" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="J8" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="K8" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="M8" s="26" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="161" hidden="1" customHeight="1">
+      <c r="A9" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="H9" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="J9" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="M9" s="26" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="72" customHeight="1">
+      <c r="A10" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="26" t="s">
+      <c r="B10" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D10" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E10" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="F8" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="43" t="s">
+      <c r="F10" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H10" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="I10" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="J8" s="40" t="s">
+      <c r="J10" s="40" t="s">
         <v>219</v>
       </c>
-      <c r="K8" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="41" t="s">
-        <v>368</v>
-      </c>
-      <c r="M8" s="26" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="161">
-      <c r="A9" s="26" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="G9" s="43" t="s">
-        <v>372</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="I9" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="J9" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="K9" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="41" t="s">
-        <v>373</v>
-      </c>
-      <c r="M9" s="26" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="72" hidden="1">
-      <c r="A10" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="I10" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="J10" s="40" t="s">
-        <v>234</v>
-      </c>
       <c r="K10" s="30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L10" s="41"/>
       <c r="M10" s="41"/>
     </row>
-    <row r="11" spans="1:13" ht="126">
+    <row r="11" spans="1:13" ht="126" hidden="1" customHeight="1">
       <c r="A11" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="J11" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="26" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="144" customHeight="1">
+      <c r="A12" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="26" t="s">
+      <c r="I12" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="J12" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="E11" s="26" t="s">
-        <v>238</v>
-      </c>
-      <c r="F11" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="J11" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="K11" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="41" t="s">
-        <v>368</v>
-      </c>
-      <c r="M11" s="26" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="144" hidden="1">
-      <c r="A12" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F12" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="H12" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="I12" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="J12" s="40" t="s">
-        <v>250</v>
-      </c>
       <c r="K12" s="30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L12" s="41"/>
       <c r="M12" s="41"/>
     </row>
-    <row r="13" spans="1:13" ht="162" hidden="1">
+    <row r="13" spans="1:13" ht="162" customHeight="1">
       <c r="A13" s="26" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="I13" s="39" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="J13" s="40" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="K13" s="30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L13" s="41"/>
       <c r="M13" s="41"/>
     </row>
-    <row r="14" spans="1:13" ht="156">
+    <row r="14" spans="1:13" ht="156" hidden="1" customHeight="1">
       <c r="A14" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="I14" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="J14" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="M14" s="26" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="146" hidden="1" customHeight="1">
+      <c r="A15" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="B14" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="26" t="s">
+      <c r="F15" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="43" t="s">
         <v>260</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="H15" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="I15" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="F14" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>379</v>
-      </c>
-      <c r="H14" s="26" t="s">
+      <c r="J15" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="K15" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="M15" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="J14" s="40" t="s">
+    </row>
+    <row r="16" spans="1:13" ht="72" hidden="1" customHeight="1">
+      <c r="A16" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="K14" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="41" t="s">
-        <v>373</v>
-      </c>
-      <c r="M14" s="26" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="146">
-      <c r="A15" s="26" t="s">
+      <c r="B16" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="26" t="s">
+      <c r="D16" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="E16" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>381</v>
-      </c>
-      <c r="F15" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="G15" s="43" t="s">
-        <v>382</v>
-      </c>
-      <c r="H15" s="26" t="s">
+      <c r="F16" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="38" t="s">
         <v>269</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="H16" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="J15" s="40" t="s">
+      <c r="I16" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="K15" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="41" t="s">
-        <v>373</v>
-      </c>
-      <c r="M15" s="26" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="72" hidden="1">
-      <c r="A16" s="26" t="s">
+      <c r="J16" s="40" t="s">
         <v>272</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>273</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="J16" s="40" t="s">
-        <v>279</v>
-      </c>
       <c r="K16" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L16" s="41"/>
       <c r="M16" s="41"/>
     </row>
-    <row r="17" spans="1:13" ht="202">
+    <row r="17" spans="1:13" ht="202" hidden="1" customHeight="1">
       <c r="A17" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="H17" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="I17" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="J17" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="K17" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="M17" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="E17" s="26" t="s">
+    </row>
+    <row r="18" spans="1:13" ht="126" hidden="1" customHeight="1">
+      <c r="A18" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="F17" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="G17" s="45" t="s">
-        <v>384</v>
-      </c>
-      <c r="H17" s="26" t="s">
+      <c r="B18" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="I17" s="39" t="s">
+      <c r="D18" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="J17" s="40" t="s">
+      <c r="E18" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="K17" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="41" t="s">
-        <v>373</v>
-      </c>
-      <c r="M17" s="26" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="126" hidden="1">
-      <c r="A18" s="26" t="s">
+      <c r="F18" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C18" s="26" t="s">
+      <c r="H18" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="I18" s="39" t="s">
         <v>289</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="J18" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="F18" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="43" t="s">
-        <v>291</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="J18" s="40" t="s">
-        <v>294</v>
-      </c>
       <c r="K18" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L18" s="41"/>
       <c r="M18" s="41"/>
     </row>
-    <row r="19" spans="1:13" ht="54">
+    <row r="19" spans="1:13" ht="54" hidden="1" customHeight="1">
       <c r="A19" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="E19" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="B19" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C19" s="26" t="s">
+      <c r="F19" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="H19" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="E19" s="26" t="s">
-        <v>386</v>
-      </c>
-      <c r="F19" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="G19" s="45" t="s">
-        <v>387</v>
-      </c>
-      <c r="H19" s="26" t="s">
+      <c r="I19" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="J19" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="J19" s="40" t="s">
+      <c r="K19" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="M19" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="K19" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="41" t="s">
-        <v>373</v>
-      </c>
-      <c r="M19" s="26" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="126">
+    </row>
+    <row r="20" spans="1:13" ht="126" hidden="1" customHeight="1">
       <c r="A20" s="26" t="s">
         <v>301</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="C20" s="26" t="s">
         <v>302</v>
@@ -4109,7 +3547,7 @@
         <v>304</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="G20" s="43" t="s">
         <v>305</v>
@@ -4124,17 +3562,17 @@
         <v>308</v>
       </c>
       <c r="K20" s="28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L20" s="41"/>
       <c r="M20" s="26"/>
     </row>
-    <row r="21" spans="1:13" ht="54" hidden="1">
+    <row r="21" spans="1:13" ht="54" customHeight="1">
       <c r="A21" s="26" t="s">
         <v>309</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="C21" s="26" t="s">
         <v>310</v>
@@ -4146,7 +3584,7 @@
         <v>312</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G21" s="43" t="s">
         <v>313</v>
@@ -4161,291 +3599,291 @@
         <v>316</v>
       </c>
       <c r="K21" s="30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L21" s="41"/>
       <c r="M21" s="41"/>
     </row>
-    <row r="22" spans="1:13" ht="216">
+    <row r="22" spans="1:13" ht="216" hidden="1" customHeight="1">
       <c r="A22" s="26" t="s">
         <v>317</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>162</v>
+        <v>318</v>
       </c>
       <c r="C22" s="26" t="s">
+        <v>319</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>320</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="F22" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="H22" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="I22" s="39" t="s">
+        <v>324</v>
+      </c>
+      <c r="J22" s="40" t="s">
+        <v>325</v>
+      </c>
+      <c r="K22" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="26" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="64" hidden="1" customHeight="1">
+      <c r="A23" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="B23" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="F22" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="G22" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>320</v>
-      </c>
-      <c r="I22" s="39" t="s">
-        <v>321</v>
-      </c>
-      <c r="J22" s="40" t="s">
-        <v>393</v>
-      </c>
-      <c r="K22" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" s="41" t="s">
-        <v>368</v>
-      </c>
-      <c r="M22" s="26" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="64">
-      <c r="A23" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>162</v>
-      </c>
       <c r="C23" s="26" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F23" s="44" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="G23" s="45" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="H23" s="26" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="I23" s="39" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="J23" s="40" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="K23" s="28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L23" s="41" t="s">
-        <v>368</v>
+        <v>24</v>
       </c>
       <c r="M23" s="26" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="59">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="59" hidden="1" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>162</v>
+        <v>318</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="G24" s="43" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J24" s="40" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="K24" s="28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L24" s="41" t="s">
-        <v>373</v>
+        <v>210</v>
       </c>
       <c r="M24" s="26" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="54" hidden="1">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="54" hidden="1" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>162</v>
+        <v>318</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="I25" s="39" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="J25" s="40" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L25" s="41"/>
       <c r="M25" s="41"/>
     </row>
-    <row r="26" spans="1:13" ht="90" hidden="1">
+    <row r="26" spans="1:13" ht="90" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G26" s="43" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="I26" s="39" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="J26" s="40" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="K26" s="30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L26" s="41"/>
       <c r="M26" s="41"/>
     </row>
-    <row r="27" spans="1:13" ht="108" hidden="1">
+    <row r="27" spans="1:13" ht="108" customHeight="1">
       <c r="A27" s="26" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G27" s="43" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="I27" s="39" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="J27" s="40" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="K27" s="30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L27" s="41"/>
       <c r="M27" s="41"/>
     </row>
-    <row r="28" spans="1:13" ht="72">
+    <row r="28" spans="1:13" ht="72" hidden="1" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="I28" s="39" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="J28" s="40" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="K28" s="28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L28" s="41" t="s">
-        <v>368</v>
+        <v>24</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M28" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <autoFilter ref="A1:M28" xr:uid="{00000000-0009-0000-0000-000001000000}">
     <filterColumn colId="10">
       <filters>
-        <filter val="低"/>
+        <filter val="中"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4455,18 +3893,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="20" style="3" customWidth="1"/>
     <col min="2" max="2" width="67.19921875" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="3"/>
+    <col min="3" max="3" width="9" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19">
+    <row r="1" spans="1:2" ht="19" customHeight="1">
       <c r="A1" s="18" t="s">
-        <v>140</v>
+        <v>377</v>
       </c>
       <c r="B1" s="18"/>
     </row>
@@ -4474,93 +3913,93 @@
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
     </row>
-    <row r="3" spans="1:2" ht="18">
+    <row r="3" spans="1:2" ht="18" customHeight="1">
       <c r="A3" s="19" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="36">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="18">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18" customHeight="1">
       <c r="A5" s="21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
     </row>
-    <row r="7" spans="1:2" ht="18">
+    <row r="7" spans="1:2" ht="18" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>144</v>
+        <v>381</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="18">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>146</v>
+        <v>383</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>147</v>
+        <v>384</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="18">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>148</v>
+        <v>385</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="22" t="s">
-        <v>149</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>150</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>151</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="25" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>152</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -4570,7 +4009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
@@ -4580,9 +4019,9 @@
     <col min="4" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19">
+    <row r="1" spans="1:8" ht="19" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>390</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4592,7 +4031,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" ht="17">
+    <row r="2" spans="1:8" ht="17" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4602,35 +4041,35 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" s="17" customFormat="1" ht="18">
+    <row r="3" spans="1:8" s="17" customFormat="1" ht="18" customHeight="1">
       <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>154</v>
+        <v>391</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>155</v>
+        <v>392</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>156</v>
+        <v>393</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="5">
         <v>0</v>
@@ -4654,9 +4093,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18">
+    <row r="5" spans="1:8" ht="18" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -4680,9 +4119,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18">
+    <row r="6" spans="1:8" ht="18" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
@@ -4706,9 +4145,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18">
+    <row r="7" spans="1:8" ht="18" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -4732,9 +4171,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18">
+    <row r="8" spans="1:8" ht="18" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="B8" s="12">
         <v>2</v>
@@ -4758,9 +4197,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18">
+    <row r="9" spans="1:8" ht="18" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>160</v>
+        <v>274</v>
       </c>
       <c r="B9" s="12">
         <v>1</v>
@@ -4784,9 +4223,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18">
+    <row r="10" spans="1:8" ht="18" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>161</v>
+        <v>292</v>
       </c>
       <c r="B10" s="12">
         <v>2</v>
@@ -4810,9 +4249,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18">
+    <row r="11" spans="1:8" ht="18" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>162</v>
+        <v>318</v>
       </c>
       <c r="B11" s="12">
         <v>3</v>
@@ -4836,9 +4275,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18">
+    <row r="12" spans="1:8" ht="18" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>163</v>
+        <v>395</v>
       </c>
       <c r="B12" s="14">
         <v>10</v>

--- a/bombus-system/docs/現況與問題比對分析_20260406.xlsx
+++ b/bombus-system/docs/現況與問題比對分析_20260406.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alifrt/Desktop/Bombus/bombus-system/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9851C6-A4D0-0747-BFE4-603A778BE84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0325E1C5-BD92-4341-8633-A37261707961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0212版修訂需求總表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="401">
   <si>
     <t>編號</t>
   </si>
@@ -1463,6 +1463,11 @@
     <t>顯示時間由「投遞日」改為「最新面試時間」（yyyy-MM-dd HH:mm 含時刻）
 AI 智能面試頁新增面試日期篩選：日期選擇器 + 快速 tabs（全部 / 今日 / 近 3 天 / 近 7 天）
 AI 智能面試頁不再顯示已進入決策階段的候選人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>為 job-descriptions.js 全部 15 個端點補上 requireFeaturePerm('L2.job-description') 中介軟體（讀取類 view、寫入與審核類 edit），修補 RBAC 漏洞：先前任何登入使用者皆可繞過前端 canEdit() 直接操作 API。一併修復 tenant-schema 與 migration 雙清單缺漏的 6 個審核欄位（current_version / rejected_reason / approved_by / approved_at / submitted_by / submitted_at），讓建立新版本、送審、核准、退回、取消封存等 JD 審核 API 真正可運作。
+範圍說明：本次為 Phase 1，以 view/edit 兩層權限區分，已可擋掉未授權存取。需求中「用人主管僅限草稿、HR 獨佔發佈」的細粒度分權屬 Phase 2，需另行以角色 gate（如 hr_admin）在 approve / publish 端點實作。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2910,7 +2915,7 @@
       <c r="L3" s="41"/>
       <c r="M3" s="41"/>
     </row>
-    <row r="4" spans="1:13" ht="72" customHeight="1">
+    <row r="4" spans="1:13" ht="215" customHeight="1">
       <c r="A4" s="26" t="s">
         <v>161</v>
       </c>
@@ -2944,8 +2949,12 @@
       <c r="K4" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
+      <c r="L4" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="M4" s="26" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="5" spans="1:13" ht="54" hidden="1" customHeight="1">
       <c r="A5" s="26" t="s">
@@ -3099,7 +3108,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="161" hidden="1" customHeight="1">
+    <row r="9" spans="1:13" ht="55" hidden="1" customHeight="1">
       <c r="A9" s="26" t="s">
         <v>202</v>
       </c>

--- a/bombus-system/docs/現況與問題比對分析_20260406.xlsx
+++ b/bombus-system/docs/現況與問題比對分析_20260406.xlsx
@@ -237,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -388,6 +388,9 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -969,7 +972,7 @@
       <c r="L3" s="50" t="n"/>
       <c r="M3" s="53" t="n"/>
     </row>
-    <row r="4" hidden="1" ht="144" customHeight="1">
+    <row r="4" ht="144" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
         <is>
           <t>D-03</t>
@@ -1104,10 +1107,18 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L5" s="50" t="n"/>
-      <c r="M5" s="53" t="n"/>
-    </row>
-    <row r="6" hidden="1" ht="126" customHeight="1">
+      <c r="L5" s="33" t="inlineStr">
+        <is>
+          <t>已修正</t>
+        </is>
+      </c>
+      <c r="M5" s="56" t="inlineStr">
+        <is>
+          <t>UUID Token 機制統一採用 UUIDv4 + DB 一次性 + 7 天效期（對齊既有 4 種 token pattern）；新增 platform DB public_tokens 索引表（token→tenant_id），讓未登入候選人能透過 token 解析到正確 tenant，並為未來公開端點（D-06 官網自薦）預留基礎。此 token 整合進 D-05 內推連結，HR 建立邀請後 API 回傳 `&lt;FRONTEND_URL&gt;/public/referral/:token` 絕對連結供複製分享，系統不寄送 email（對齊既有 responseLink/cancelLink 手動分享模式）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="126" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
           <t>D-05</t>
@@ -1166,10 +1177,29 @@
           <t>高</t>
         </is>
       </c>
-      <c r="L6" s="34" t="n"/>
-      <c r="M6" s="34" t="n"/>
-    </row>
-    <row r="7" hidden="1" ht="126" customHeight="1">
+      <c r="L6" s="33" t="inlineStr">
+        <is>
+          <t>已修正</t>
+        </is>
+      </c>
+      <c r="M6" s="56" t="inlineStr">
+        <is>
+          <t>實作「HR 代發起內部推薦」完整流程：
+後端：
+- 新 routes：recruitment-referrals.js（HR CRUD + /renew 延長並重取連結 + /recommender-preview 即時驗員編）、public-referrals.js（候選人 GET/:token + POST submit，經 platform public_tokens 解析 tenant）、candidate-attachments.js（HR + 公開 token 版檔案上傳，pdf/doc/image 10MB，修正 multer 中文檔名亂碼）、recruitment-candidates.js（HR 新增候選人 API，原為 TODO）
+- 新 service：candidate-write.service.js（共用寫入 candidates + 6 張關聯表 education/experience/speciality/language/project/attachment，含 summary 欄位自動推導 current_company、current_position、seniority「X年Y個月」）
+- tenant schema：新增 referral_invitations 表（id/token/job_id/recommender_employee_id/candidate_email/status/expires_at/submitted_at 等），candidates 表加 source_detail JSON；tenant-schema + tenant-db-manager 雙遷移清單同步；org_unit.js 共用往上找 subsidiary/group 工具
+前端：
+- 新共用元件 shared/components/candidate-full-form/（4 tabs：基本資料/求職條件/學經歷/技能與作品，對齊 104 欄位；HR modal + 公開內推頁共用，節省 ~460 行 jobs-page inline form）
+- 欄位 UI：國籍/語言 select、聯絡方式 select、駕照/交通工具 multi-select chips、個人特色/技能標籤/相關標籤 tag input（建立按鈕 + Enter + chip 下方顯示 + × 移除）、大頭照上傳含拖曳定位 + 縮放 + canvas 裁切至 320px
+- 內推 Modal (referral-invitation-modal)：tab 建立新邀請 / 歷史邀請（清單含複製連結 / 延長 7 天 / 取消），推薦人員編 debounce 預覽顯示「姓名｜公司｜部門｜職稱」
+- 候選人列表卡片：內推/104/手動 chip + 推薦人 tooltip、學經歷摘要（seniority 年月）、應徵日期格式化 YYYY/MM/DD；履歷詳情頁語言能力顯示聽說讀寫級距
+- 公開頁 /public/referral/:token 與 referral-invalid / referral-success 完整流程
+對齊業主需求：D-04 連結產生 + 候選人欄位對齊 104 + 必要資訊必填其餘選填 + 工作經歷改選填 + 技能/語言各至少 1 筆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="126" customHeight="1">
       <c r="A7" s="26" t="inlineStr">
         <is>
           <t>D-06</t>
@@ -1249,12 +1279,12 @@
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>發送面試邀約時同步確認面試官行程是否有空，可考慮 ICS 串接。公司沒有自己信箱時要考慮如何避免時段重複</t>
+          <t>發送面試邀約時同步確認面試官行程是否有空，並且要考慮如何避免時段重複</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>面試排程時需檢查面試官行事曆衝突，建議透過 ICS 格式串接企業行事曆；無企業信箱時需系統內建衝突檢測</t>
+          <t>面試排程時需檢查面試官行事曆衝突；無企業信箱時需系統內建衝突檢測</t>
         </is>
       </c>
       <c r="F8" s="29" t="inlineStr">
@@ -1310,7 +1340,7 @@
         </is>
       </c>
     </row>
-    <row r="9" hidden="1" ht="108" customHeight="1">
+    <row r="9" ht="108" customHeight="1">
       <c r="A9" s="26" t="inlineStr">
         <is>
           <t>D-08</t>
@@ -1481,9 +1511,9 @@
           <t>新增「今日面試摘要區」供面試官快速掌握當日面試；Tab 簡化為三個以面試為中心的狀態分類</t>
         </is>
       </c>
-      <c r="F11" s="29" t="inlineStr">
-        <is>
-          <t>⚠️ 部分實作</t>
+      <c r="F11" s="27" t="inlineStr">
+        <is>
+          <t>✅ 已實作</t>
         </is>
       </c>
       <c r="G11" s="26" t="inlineStr">
@@ -1531,7 +1561,7 @@
         </is>
       </c>
     </row>
-    <row r="12" hidden="1" ht="234" customHeight="1">
+    <row r="12" ht="234" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
           <t>D-11</t>
@@ -1755,7 +1785,7 @@
         </is>
       </c>
     </row>
-    <row r="15" hidden="1" ht="180" customHeight="1">
+    <row r="15" ht="180" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
           <t>D-14</t>
@@ -1906,6 +1936,7 @@
     <filterColumn colId="10" hiddenButton="0" showButton="1">
       <filters>
         <filter val="中"/>
+        <filter val="高"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3841,8 +3872,8 @@
   <cols>
     <col width="20" customWidth="1" style="3" min="1" max="1"/>
     <col width="67.19921875" customWidth="1" style="3" min="2" max="2"/>
-    <col width="9" customWidth="1" style="3" min="3" max="4"/>
-    <col width="9" customWidth="1" style="3" min="5" max="16384"/>
+    <col width="9" customWidth="1" style="3" min="3" max="5"/>
+    <col width="9" customWidth="1" style="3" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="19" customHeight="1">

--- a/bombus-system/docs/現況與問題比對分析_20260406.xlsx
+++ b/bombus-system/docs/現況與問題比對分析_20260406.xlsx
@@ -111,8 +111,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Apple Color Emoji"/>
-      <charset val="136"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -237,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -381,17 +380,20 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -759,7 +761,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -770,7 +772,7 @@
     <col width="40" customWidth="1" min="8" max="10"/>
     <col width="20.3984375" customWidth="1" min="11" max="11"/>
     <col width="15.3984375" customWidth="1" style="51" min="12" max="12"/>
-    <col width="104.3984375" customWidth="1" style="54" min="13" max="13"/>
+    <col width="104.3984375" customWidth="1" style="56" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customFormat="1" customHeight="1" s="35">
@@ -969,8 +971,22 @@
           <t>中</t>
         </is>
       </c>
-      <c r="L3" s="50" t="n"/>
-      <c r="M3" s="53" t="n"/>
+      <c r="L3" s="57" t="inlineStr">
+        <is>
+          <t>已修正</t>
+        </is>
+      </c>
+      <c r="M3" s="11" t="inlineStr">
+        <is>
+          <t>已完成多平台職缺發布架構（D-02/D-03 骨架）：
+• 資料層新增 job_publications (1:N) + 雙遷移清單，既有 job104_no 冪等遷移
+• 後端 platform-publisher Strategy Pattern：104 adapter 包裝既有 service；518/1111 stub（NOT_IMPLEMENTED）
+• routes/jobs.js 改走 Promise.allSettled 並行：publish / update / close / delete 各平台獨立狀態
+• 新增 POST /api/jobs/:jobId/publications/:platform/retry 單平台重試端點
+• 前端移除 dataSource Tab，改為 per-platform chip + 詳情/重試 Modal；Filter bar 新增平台篩選
+• 職缺基礎能力（新增候選人/內推/關閉）與外部發布解耦，不因 job.source 差別隱藏按鈕</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="144" customHeight="1">
       <c r="A4" s="26" t="inlineStr">
@@ -1035,8 +1051,23 @@
           <t>高</t>
         </is>
       </c>
-      <c r="L4" s="34" t="n"/>
-      <c r="M4" s="34" t="n"/>
+      <c r="L4" s="57" t="inlineStr">
+        <is>
+          <t>部分修正</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>D-03 的架構彈性部分已完成：
+• platform-publisher 抽象介面 + registry + enabled/supported list，加新平台僅需實作 adapter
+• 518/1111 UI 預留 checkbox（disabled + tooltip「平台尚未開放」），啟用只需補 adapter 實作
+• 104 adapter 15s timeout wrapper，單平台超時不拖累整體
+• jobs.js 路由不認識特定平台，符合「新增來源不需改核心程式」原則
+未完成（留待後續）：
+• 定時自動同步引擎（cron / scheduler）— 本次僅提供手動「重試同步」按鈕
+• 從外部平台拉取候選人履歷（104 Resume API 串接）— UI 已預留入口，實際整合另立 job-104-candidate-sync 變更</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="180" customHeight="1">
       <c r="A5" s="26" t="inlineStr">
@@ -1112,13 +1143,13 @@
           <t>已修正</t>
         </is>
       </c>
-      <c r="M5" s="56" t="inlineStr">
+      <c r="M5" s="53" t="inlineStr">
         <is>
           <t>UUID Token 機制統一採用 UUIDv4 + DB 一次性 + 7 天效期（對齊既有 4 種 token pattern）；新增 platform DB public_tokens 索引表（token→tenant_id），讓未登入候選人能透過 token 解析到正確 tenant，並為未來公開端點（D-06 官網自薦）預留基礎。此 token 整合進 D-05 內推連結，HR 建立邀請後 API 回傳 `&lt;FRONTEND_URL&gt;/public/referral/:token` 絕對連結供複製分享，系統不寄送 email（對齊既有 responseLink/cancelLink 手動分享模式）。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="126" customHeight="1">
+    <row r="6" ht="409" customHeight="1">
       <c r="A6" s="26" t="inlineStr">
         <is>
           <t>D-05</t>
@@ -1182,7 +1213,7 @@
           <t>已修正</t>
         </is>
       </c>
-      <c r="M6" s="56" t="inlineStr">
+      <c r="M6" s="53" t="inlineStr">
         <is>
           <t>實作「HR 代發起內部推薦」完整流程：
 後端：
@@ -1259,7 +1290,7 @@
         </is>
       </c>
       <c r="L7" s="34" t="n"/>
-      <c r="M7" s="34" t="n"/>
+      <c r="M7" s="55" t="n"/>
     </row>
     <row r="8" ht="144" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
@@ -1334,7 +1365,7 @@
           <t>已修正</t>
         </is>
       </c>
-      <c r="M8" s="53" t="inlineStr">
+      <c r="M8" s="54" t="inlineStr">
         <is>
           <t>發邀約頁新增面試官選擇下拉（姓名｜部門｜職稱，依職缺部門預設篩選+fallback）、建議時段即時衝突標示；安排面試時段頁面試官改唯讀；時間拆為時/分兩個下拉強制 15 分鐘粒度；後端新增 check-conflicts API（面試官+候選人雙向，meetings 鏡像去重），invitations/interviews 建立前衝突硬擋回 409；面試建立/取消同 transaction 同步 meetings 鏡像紀錄；interview_invitations 加 interviewer_id 欄位與 FK，demo seed 重建映射到真實員工。</t>
         </is>
@@ -1399,7 +1430,7 @@
         </is>
       </c>
       <c r="L9" s="34" t="n"/>
-      <c r="M9" s="34" t="n"/>
+      <c r="M9" s="55" t="n"/>
     </row>
     <row r="10" ht="399" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
@@ -1470,7 +1501,7 @@
           <t>已修正</t>
         </is>
       </c>
-      <c r="M10" s="55" t="inlineStr">
+      <c r="M10" s="53" t="inlineStr">
         <is>
           <t>後端：jobs.js PUT /:id 偵測 7 個關鍵欄位（title/department/description/jd_id/grade/org_unit_id/job104_data）變動，published 狀態自動回 review、清 publish_date、patchJobStatus(off) 關閉 104；新增 GET /:id/candidates-summary；DELETE 三層防護：
 L1 HAS_ONBOARDED_CANDIDATES（已轉入職）→ 永不允許
@@ -1553,7 +1584,7 @@
           <t>已修正</t>
         </is>
       </c>
-      <c r="M11" s="53" t="inlineStr">
+      <c r="M11" s="54" t="inlineStr">
         <is>
           <t>顯示時間由「投遞日」改為「最新面試時間」（yyyy-MM-dd HH:mm 含時刻）
 AI 智能面試頁新增面試日期篩選：日期選擇器 + 快速 tabs（全部 / 今日 / 近 3 天 / 近 7 天）
@@ -1630,7 +1661,7 @@
         </is>
       </c>
       <c r="L12" s="34" t="n"/>
-      <c r="M12" s="34" t="n"/>
+      <c r="M12" s="55" t="n"/>
     </row>
     <row r="13" ht="216" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
@@ -1702,7 +1733,7 @@
           <t>已修正</t>
         </is>
       </c>
-      <c r="M13" s="53" t="inlineStr">
+      <c r="M13" s="54" t="inlineStr">
         <is>
           <t>拆分至獨立「面試決策」頁 (/employee/decision)，新增 L1.decision feature；RBAC：super_admin / subsidiary_admin / hr_manager = edit；dept_manager / employee = none。Tab 調整為 全部/待決策/已決策。</t>
         </is>
@@ -1779,7 +1810,7 @@
           <t>已修正</t>
         </is>
       </c>
-      <c r="M14" s="53" t="inlineStr">
+      <c r="M14" s="54" t="inlineStr">
         <is>
           <t>決策頁重構為：① 候選人基本資料 ② 職缺詳情（職等/薪資範圍/期望薪資/JD 摘要）③ 面試評分（只讀）④ AI 量化分析（只讀）⑤ 錄用決策 + 薪資核定（類型/金額，依 job.grade 關聯 grade_salary_levels 顯示範圍，超範圍警告但仍可送）。</t>
         </is>
@@ -1853,7 +1884,7 @@
         </is>
       </c>
       <c r="L15" s="34" t="n"/>
-      <c r="M15" s="34" t="n"/>
+      <c r="M15" s="55" t="n"/>
     </row>
     <row r="16" ht="216" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
@@ -1925,7 +1956,7 @@
           <t>已修正</t>
         </is>
       </c>
-      <c r="M16" s="53" t="inlineStr">
+      <c r="M16" s="54" t="inlineStr">
         <is>
           <t>新增主管簽核流程：HR 送簽 → subsidiary_admin 簽核 → offered（產 UUID offer link），可無限次退回重送。入職轉換（convert-candidate）要求 approval_status = APPROVED，既有資料 NONE 豁免。</t>
         </is>
@@ -3872,8 +3903,8 @@
   <cols>
     <col width="20" customWidth="1" style="3" min="1" max="1"/>
     <col width="67.19921875" customWidth="1" style="3" min="2" max="2"/>
-    <col width="9" customWidth="1" style="3" min="3" max="5"/>
-    <col width="9" customWidth="1" style="3" min="6" max="16384"/>
+    <col width="9" customWidth="1" style="3" min="3" max="6"/>
+    <col width="9" customWidth="1" style="3" min="7" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="19" customHeight="1">
